--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484175_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484175_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3898</v>
+        <v>5.0554</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0018</v>
+        <v>3.3906</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3881</v>
+        <v>1.6648</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3038</v>
+        <v>1.4128</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3487</v>
+        <v>0.1664</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9552</v>
+        <v>1.2464</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1683</v>
+        <v>2.0165</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0076</v>
+        <v>1.8909</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1606</v>
+        <v>0.1256</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1355</v>
+        <v>-0.6037</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.659</v>
+        <v>-1.7245</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7945</v>
+        <v>1.1208</v>
       </c>
       <c r="P2" t="n">
         <v>-0.9919</v>
@@ -610,28 +610,28 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>5.7407</v>
+        <v>0.4832</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8092</v>
+        <v>0.1985</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9314</v>
+        <v>0.2846</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3373</v>
+        <v>4.1513</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4.1513</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3515</v>
+        <v>4.1119</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2659</v>
+        <v>0.6777</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0856</v>
+        <v>3.4342</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4128</v>
+        <v>2.3038</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1664</v>
+        <v>0.3487</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2464</v>
+        <v>1.9552</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0165</v>
+        <v>2.1683</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8909</v>
+        <v>2.0076</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1256</v>
+        <v>0.1606</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6037</v>
+        <v>0.1355</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7245</v>
+        <v>-1.659</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1208</v>
+        <v>1.7945</v>
       </c>
       <c r="P3" t="n">
         <v>-0.9919</v>
@@ -688,22 +688,22 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7793</v>
+        <v>2.4628</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0738</v>
+        <v>1.4852</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7055</v>
+        <v>0.9776</v>
       </c>
       <c r="V3" t="n">
-        <v>4.1513</v>
+        <v>0.3373</v>
       </c>
       <c r="W3" t="n">
-        <v>4.1513</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8092</v>
+        <v>3.2541</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1439</v>
+        <v>1.3083</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6653</v>
+        <v>1.9458</v>
       </c>
       <c r="G4" t="n">
         <v>3.0128</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9296</v>
+        <v>-0.4846</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3627</v>
+        <v>-0.1983</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5669</v>
+        <v>-0.2863</v>
       </c>
       <c r="V4" t="n">
         <v>-0.266</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. CEBRIA PUCHADES</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2055</v>
+        <v>0.7063</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3064</v>
+        <v>0.8708</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1009</v>
+        <v>-0.1645</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2151</v>
+        <v>2.7621</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4034</v>
+        <v>0.7165</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6185</v>
+        <v>2.0457</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5907</v>
+        <v>2.2201</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0605</v>
+        <v>2.3705</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5302</v>
+        <v>-0.1504</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6244</v>
+        <v>0.542</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4639</v>
+        <v>-1.6541</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0883</v>
+        <v>2.1961</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6127</v>
+        <v>0.3571</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3004</v>
+        <v>0.3686</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3124</v>
+        <v>-0.0115</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2065</v>
+        <v>-2.4129</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0403</v>
+        <v>0.6728</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4326</v>
+        <v>-1.0244</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4728</v>
+        <v>1.6973</v>
       </c>
       <c r="G6" t="n">
         <v>2.1457</v>
@@ -922,13 +922,13 @@
         <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0261</v>
+        <v>0.6065</v>
       </c>
       <c r="T6" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.4762</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.1303</v>
       </c>
       <c r="V6" t="n">
         <v>-1.881</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>V. CEBRIA PUCHADES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5815</v>
+        <v>0.3521</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0319</v>
+        <v>0.3688</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.0167</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7621</v>
+        <v>3.2151</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7165</v>
+        <v>-0.4034</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0457</v>
+        <v>3.6185</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2201</v>
+        <v>2.5907</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3705</v>
+        <v>0.0605</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1504</v>
+        <v>2.5302</v>
       </c>
       <c r="M7" t="n">
-        <v>0.542</v>
+        <v>0.6244</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6541</v>
+        <v>-0.4639</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1961</v>
+        <v>1.0883</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9307</v>
+        <v>-0.4662</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4703</v>
+        <v>-0.238</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4604</v>
+        <v>-0.2282</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4129</v>
+        <v>-1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6789</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2511</v>
+        <v>-1.121</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4026</v>
+        <v>-1.3005</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1515</v>
+        <v>0.1796</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2698</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0187</v>
+        <v>0.1488</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U8" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5556</v>
+        <v>-1.4255</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.235</v>
+        <v>-1.133</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3205</v>
+        <v>-0.2925</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1184</v>
@@ -1156,13 +1156,13 @@
         <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1661</v>
+        <v>0.2962</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1871</v>
       </c>
       <c r="U9" t="n">
-        <v>0.081</v>
+        <v>0.1091</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MESADO PLANELLS</t>
+          <t>J. ROSA DE SOUSA DA SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.097</v>
+        <v>-1.5754</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8056</v>
+        <v>-3.3531</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2914</v>
+        <v>1.7777</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1557</v>
+        <v>-2.0152</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7409</v>
+        <v>-0.2479</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8966</v>
+        <v>-1.7674</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0591</v>
+        <v>-1.754</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4542</v>
+        <v>1.2702</v>
       </c>
       <c r="L10" t="n">
-        <v>0.605</v>
+        <v>-3.0242</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9035</v>
+        <v>-0.2612</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.195</v>
+        <v>-1.518</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2916</v>
+        <v>1.2569</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9919</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>2.3806</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6575</v>
+        <v>-0.1715</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1191</v>
+        <v>0.1702</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7766</v>
+        <v>-0.3417</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. SERRA DE MUNTER</t>
+          <t>J. MESADO PLANELLS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4886</v>
+        <v>-1.9581</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7567</v>
+        <v>-0.9473</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7318</v>
+        <v>-1.0108</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1875</v>
+        <v>0.1557</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1187</v>
+        <v>-0.7409</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0688</v>
+        <v>0.8966</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6546999999999999</v>
+        <v>1.0591</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6546999999999999</v>
+        <v>0.4542</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.605</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5327</v>
+        <v>-0.9035</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4639</v>
+        <v>-1.195</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0688</v>
+        <v>0.2916</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.293</v>
+        <v>-0.5187</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.102</v>
+        <v>-0.0226</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.191</v>
+        <v>-0.496</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6032</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOUSA DA SILVA</t>
+          <t>F. SERRA DE MUNTER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.732</v>
+        <v>-2.3585</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5378</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8058</v>
+        <v>-1.7038</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0152</v>
+        <v>-2.1875</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2479</v>
+        <v>-1.1187</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7674</v>
+        <v>-1.0688</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.754</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2702</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.0242</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2612</v>
+        <v>-1.5327</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.518</v>
+        <v>-0.4639</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2569</v>
+        <v>-1.0688</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5952</v>
+        <v>0.5952</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3806</v>
+        <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3281</v>
+        <v>-0.1629</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0145</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3136</v>
+        <v>-0.163</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2065</v>
+        <v>-0.6032</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.090499999999998</v>
+        <v>5.714100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.420399999999999</v>
+        <v>-1.7968</v>
       </c>
       <c r="F13" t="n">
-        <v>7.511100000000001</v>
+        <v>7.5111</v>
       </c>
       <c r="G13" t="n">
         <v>7.4171</v>
@@ -1441,7 +1441,7 @@
         <v>10.1379</v>
       </c>
       <c r="J13" t="n">
-        <v>6.658100000000001</v>
+        <v>6.6581</v>
       </c>
       <c r="K13" t="n">
         <v>6.2054</v>
@@ -1450,7 +1450,7 @@
         <v>0.4526999999999997</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7591</v>
+        <v>0.7591000000000003</v>
       </c>
       <c r="N13" t="n">
         <v>-8.9261</v>
@@ -1468,13 +1468,13 @@
         <v>12.8948</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9271</v>
+        <v>2.5507</v>
       </c>
       <c r="T13" t="n">
-        <v>1.843</v>
+        <v>2.4666</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08379999999999982</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2777</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9829</v>
+        <v>4.6929</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6092</v>
+        <v>1.6909</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3737</v>
+        <v>3.002</v>
       </c>
       <c r="G14" t="n">
         <v>1.9344</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2035</v>
+        <v>-0.0864</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8787</v>
+        <v>-0.0395</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6752</v>
+        <v>-0.0469</v>
       </c>
       <c r="V14" t="n">
         <v>0.266</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6599</v>
+        <v>2.8818</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7709</v>
+        <v>4.077</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1111</v>
+        <v>-1.1953</v>
       </c>
       <c r="G15" t="n">
         <v>0.9111</v>
@@ -1624,13 +1624,13 @@
         <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5504</v>
+        <v>0.7723</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1928</v>
+        <v>0.4989</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3576</v>
+        <v>0.2734</v>
       </c>
       <c r="V15" t="n">
         <v>0.6032</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5273</v>
+        <v>1.2219</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.0125</v>
+        <v>-3.1145</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5398</v>
+        <v>4.3364</v>
       </c>
       <c r="G16" t="n">
         <v>1.3277</v>
@@ -1702,13 +1702,13 @@
         <v>2.3806</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6058</v>
+        <v>-0.9112</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5554</v>
+        <v>-0.6574</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0504</v>
+        <v>-0.2538</v>
       </c>
       <c r="V16" t="n">
         <v>0.4085</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3449</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7163</v>
+        <v>-0.5122</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0612</v>
+        <v>1.1649</v>
       </c>
       <c r="G17" t="n">
         <v>1.8337</v>
@@ -1780,13 +1780,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2823</v>
+        <v>0.0255</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1189</v>
+        <v>0.0851</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1634</v>
+        <v>-0.0596</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2065</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5884</v>
+        <v>0.5501</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.3621</v>
+        <v>-2.8519</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7737</v>
+        <v>3.402</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6889</v>
@@ -1858,13 +1858,13 @@
         <v>2.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.701</v>
+        <v>-0.5626</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2242</v>
+        <v>-0.7141</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4768</v>
+        <v>0.1515</v>
       </c>
       <c r="V18" t="n">
         <v>1.2065</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0905</v>
+        <v>-2.2452</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3272</v>
+        <v>-2.6333</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2367</v>
+        <v>0.3881</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7598</v>
@@ -1936,13 +1936,13 @@
         <v>2.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.645</v>
+        <v>0.4903</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0395</v>
+        <v>-0.3456</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6845</v>
+        <v>0.8359</v>
       </c>
       <c r="V19" t="n">
         <v>2.4129</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>J. CAÑELLAS VAQUÉ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6525</v>
+        <v>-3.0548</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6897</v>
+        <v>-0.3145</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9628</v>
+        <v>-2.7404</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.4573</v>
+        <v>-1.3986</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6656</v>
+        <v>-0.8118</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7917</v>
+        <v>-0.5869</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3247</v>
+        <v>-0.4789</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7248</v>
+        <v>0.121</v>
       </c>
       <c r="L20" t="n">
         <v>-0.5999</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1327</v>
+        <v>-0.9197</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9408</v>
+        <v>-0.9327</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1918</v>
+        <v>0.013</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0032</v>
+        <v>-0.2352</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6269</v>
+        <v>0.1644</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3763</v>
+        <v>-0.3996</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CAÑELLAS VAQUÉ</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9374</v>
+        <v>-3.4228</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0287</v>
+        <v>-1.4039</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9087</v>
+        <v>-2.0189</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3986</v>
+        <v>-4.4573</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8118</v>
+        <v>-2.6656</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5869</v>
+        <v>-1.7917</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4789</v>
+        <v>-1.3247</v>
       </c>
       <c r="K21" t="n">
-        <v>0.121</v>
+        <v>-0.7248</v>
       </c>
       <c r="L21" t="n">
         <v>-0.5999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9197</v>
+        <v>-3.1327</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9327</v>
+        <v>-1.9408</v>
       </c>
       <c r="O21" t="n">
-        <v>0.013</v>
+        <v>-1.1918</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1177</v>
+        <v>1.2329</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5498</v>
+        <v>0.9127</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.3202</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3368</v>
+        <v>-3.6464</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7547</v>
+        <v>-2.4486</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5821</v>
+        <v>-1.1978</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1193</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6223</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2946</v>
+        <v>0.0115</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3277</v>
+        <v>0.0566</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.090600000000002</v>
+        <v>-2.3698</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.511099999999999</v>
+        <v>-7.511</v>
       </c>
       <c r="F23" t="n">
-        <v>2.420399999999999</v>
+        <v>5.141000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-7.417000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>15.8707</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.927</v>
+        <v>0.7937000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.08399999999999974</v>
+        <v>-0.08399999999999992</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8431</v>
+        <v>0.8776999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.2777</v>
